--- a/leave_of_absence_forms/011_urban_development_symposium_leave_of_absence_form--leave_of_absence_forms.xlsx
+++ b/leave_of_absence_forms/011_urban_development_symposium_leave_of_absence_form--leave_of_absence_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>start date</t>
         </is>
       </c>
     </row>
@@ -1190,75 +1190,75 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>end date</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>absence_dates_choices</t>
+          <t>timezone_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>absence_dates_choices</t>
+          <t>timezone_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>edt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>EDT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>absence_dates_choices</t>
+          <t>timezone_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>pdt</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>PDT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>absence_dates_choices</t>
+          <t>timezone_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>pst</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>end_date</t>
+          <t>PST</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>est</t>
+          <t>cst</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>CST</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>edt</t>
+          <t>cdt</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EDT</t>
+          <t>CDT</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pdt</t>
+          <t>mst</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PDT</t>
+          <t>MST</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>pst</t>
+          <t>mdt</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PST</t>
+          <t>MDT</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cst</t>
+          <t>gmt</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CST</t>
+          <t>GMT</t>
         </is>
       </c>
     </row>
@@ -1355,78 +1355,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cdt</t>
+          <t>utc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>CDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>timezone_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>mst</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>MST</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>timezone_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>mdt</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>timezone_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>gmt</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GMT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>timezone_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>utc</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>UTC</t>
         </is>
